--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484856_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484856_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2937</v>
+        <v>4.8066</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2836</v>
+        <v>3.7965</v>
       </c>
       <c r="F2" t="n">
         <v>1.0101</v>
@@ -610,10 +610,10 @@
         <v>1.1322</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6301</v>
+        <v>1.1429</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5966</v>
+        <v>0.1094</v>
       </c>
       <c r="U2" t="n">
         <v>1.0335</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4903</v>
+        <v>1.2216</v>
       </c>
       <c r="E3" t="n">
-        <v>5.92</v>
+        <v>3.3867</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.4297</v>
+        <v>-2.1652</v>
       </c>
       <c r="G3" t="n">
         <v>-3.7263</v>
@@ -688,13 +688,13 @@
         <v>1.3209</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3488</v>
+        <v>2.08</v>
       </c>
       <c r="T3" t="n">
-        <v>3.668</v>
+        <v>1.1347</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6808</v>
+        <v>0.9453</v>
       </c>
       <c r="V3" t="n">
         <v>2.4904</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2617</v>
+        <v>0.2132</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0076</v>
+        <v>0.4409</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2541</v>
+        <v>-0.2276</v>
       </c>
       <c r="G4" t="n">
         <v>0.0036</v>
@@ -766,13 +766,13 @@
         <v>0.3774</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3598</v>
+        <v>0.1152</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4703</v>
+        <v>-0.0218</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1105</v>
+        <v>0.137</v>
       </c>
       <c r="V4" t="n">
         <v>0.6606</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2685</v>
+        <v>-0.111</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4138</v>
+        <v>0.0348</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1453</v>
+        <v>-0.1457</v>
       </c>
       <c r="G5" t="n">
         <v>-0.197</v>
@@ -844,13 +844,13 @@
         <v>0.3774</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1928</v>
+        <v>0.3504</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5879</v>
+        <v>-0.1394</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.4897</v>
       </c>
       <c r="V5" t="n">
         <v>0.3018</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5823</v>
+        <v>-0.5294</v>
       </c>
       <c r="E6" t="n">
         <v>-0.6661</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0838</v>
+        <v>0.1367</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5588</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0235</v>
+        <v>0.0294</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0588</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0353</v>
+        <v>0.0882</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0976</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2127</v>
+        <v>-1.0178</v>
       </c>
       <c r="F7" t="n">
         <v>0.1151</v>
@@ -1000,10 +1000,10 @@
         <v>1.1322</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2403</v>
+        <v>1.4352</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1822</v>
+        <v>0.377</v>
       </c>
       <c r="U7" t="n">
         <v>1.0582</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5027</v>
+        <v>-2.197</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6841</v>
+        <v>-1.4048</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8186</v>
+        <v>-0.7922</v>
       </c>
       <c r="G8" t="n">
         <v>-2.6555</v>
@@ -1078,13 +1078,13 @@
         <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3414</v>
+        <v>0.6472</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3608</v>
+        <v>0.6401</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0194</v>
+        <v>0.0071</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5749</v>
+        <v>-2.7463</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1726</v>
+        <v>-1.5292</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4023</v>
+        <v>-1.2171</v>
       </c>
       <c r="G9" t="n">
         <v>-4.3725</v>
@@ -1156,13 +1156,13 @@
         <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0893</v>
+        <v>-0.2607</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8818</v>
+        <v>-0.2384</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2075</v>
+        <v>-0.0223</v>
       </c>
       <c r="V9" t="n">
         <v>0.9434</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4933</v>
+        <v>-3.0331</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8621</v>
+        <v>-1.6928</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6313</v>
+        <v>-1.3403</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9627</v>
@@ -1234,13 +1234,13 @@
         <v>1.1322</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8889</v>
+        <v>0.5714</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1758</v>
+        <v>-0.0065</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2869</v>
+        <v>0.5779</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3564</v>
+        <v>-4.7814</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0329</v>
+        <v>-3.9024</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3234</v>
+        <v>-0.879</v>
       </c>
       <c r="G11" t="n">
         <v>-3.772</v>
@@ -1312,13 +1312,13 @@
         <v>1.3209</v>
       </c>
       <c r="S11" t="n">
-        <v>0.227</v>
+        <v>0.802</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3521</v>
+        <v>-0.2216</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5791</v>
+        <v>1.0235</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2452</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.353400000000001</v>
+        <v>-8.0595</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8483</v>
+        <v>-2.554200000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.505100000000001</v>
+        <v>-5.5052</v>
       </c>
       <c r="G12" t="n">
         <v>-16.8398</v>
@@ -1390,13 +1390,13 @@
         <v>8.4915</v>
       </c>
       <c r="S12" t="n">
-        <v>6.6189</v>
+        <v>6.913</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2809</v>
+        <v>1.5747</v>
       </c>
       <c r="U12" t="n">
-        <v>5.338100000000001</v>
+        <v>5.3381</v>
       </c>
       <c r="V12" t="n">
         <v>4.697999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.4448</v>
+        <v>6.9307</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5077</v>
+        <v>5.7025</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9371</v>
+        <v>1.2281</v>
       </c>
       <c r="G13" t="n">
         <v>4.238</v>
@@ -1468,13 +1468,13 @@
         <v>1.6983</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.0951</v>
+        <v>-1.6092</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3521</v>
+        <v>-1.1572</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.743</v>
+        <v>-0.452</v>
       </c>
       <c r="V13" t="n">
         <v>2.7922</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W. LADSON BUGALLO</t>
+          <t>J. ESTRELLA MATOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7933</v>
+        <v>1.8702</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0793</v>
+        <v>0.7245</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.286</v>
+        <v>1.1457</v>
       </c>
       <c r="G14" t="n">
-        <v>3.897</v>
+        <v>3.3319</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2971</v>
+        <v>4.791</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5999</v>
+        <v>-1.4591</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9024</v>
+        <v>2.553</v>
       </c>
       <c r="K14" t="n">
-        <v>2.779</v>
+        <v>4.3371</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1234</v>
+        <v>-1.7842</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9946</v>
+        <v>0.779</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5181</v>
+        <v>0.4539</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4765</v>
+        <v>0.325</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9435</v>
+        <v>0.7548</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9435</v>
+        <v>1.6983</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5002</v>
+        <v>-0.3108</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.823</v>
+        <v>-0.2244</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6771</v>
+        <v>-0.0864</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.547</v>
+        <v>-1.9058</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-0.6606</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.547</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. ZOROA GARCIA</t>
+          <t>W. LADSON BUGALLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7456</v>
+        <v>1.7933</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2859</v>
+        <v>2.0793</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4596</v>
+        <v>-0.286</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7649</v>
+        <v>3.897</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0268</v>
+        <v>3.2971</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2618</v>
+        <v>0.5999</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3935</v>
+        <v>2.9024</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3523</v>
+        <v>2.779</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0411</v>
+        <v>0.1234</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6284999999999999</v>
+        <v>0.9946</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3256</v>
+        <v>0.5181</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.303</v>
+        <v>0.4765</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.3774</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1693</v>
+        <v>-1.5002</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3527</v>
+        <v>-0.823</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5221</v>
+        <v>-0.6771</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6226</v>
+        <v>-1.547</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>E. ZOROA GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5657</v>
+        <v>1.5075</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7603</v>
+        <v>1.2859</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1947</v>
+        <v>0.2216</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6539</v>
+        <v>0.7649</v>
       </c>
       <c r="H16" t="n">
-        <v>1.091</v>
+        <v>1.0268</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5629</v>
+        <v>-0.2618</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1735</v>
+        <v>1.3935</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9141</v>
+        <v>1.3523</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2595</v>
+        <v>0.0411</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4804</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1769</v>
+        <v>-0.3256</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3035</v>
+        <v>-0.303</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3774</v>
+        <v>0.1887</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1322</v>
+        <v>-0.3774</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5096</v>
+        <v>0.5661</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2204</v>
+        <v>-0.0688</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5262</v>
+        <v>-0.3527</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3058</v>
+        <v>0.284</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2452</v>
+        <v>0.6226</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2452</v>
+        <v>0.6226</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ESTRELLA MATOS</t>
+          <t>M. MARISCAL GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.472</v>
+        <v>1.3057</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4322</v>
+        <v>1.602</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0399</v>
+        <v>-0.2963</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3319</v>
+        <v>3.0151</v>
       </c>
       <c r="H17" t="n">
-        <v>4.791</v>
+        <v>-0.8491</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.4591</v>
+        <v>3.8642</v>
       </c>
       <c r="J17" t="n">
-        <v>2.553</v>
+        <v>2.7514</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3371</v>
+        <v>-0.5064</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.7842</v>
+        <v>3.2578</v>
       </c>
       <c r="M17" t="n">
-        <v>0.779</v>
+        <v>0.2637</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4539</v>
+        <v>-0.3428</v>
       </c>
       <c r="O17" t="n">
-        <v>0.325</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="P17" t="n">
         <v>0.7548</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9435</v>
+        <v>-0.3774</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6983</v>
+        <v>1.1322</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7089</v>
+        <v>-0.9172</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5168</v>
+        <v>-0.772</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1922</v>
+        <v>-0.1451</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.9058</v>
+        <v>-1.547</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6606</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2452</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0137</v>
+        <v>1.1376</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0684</v>
+        <v>0.0291</v>
       </c>
       <c r="F18" t="n">
-        <v>1.082</v>
+        <v>1.1085</v>
       </c>
       <c r="G18" t="n">
         <v>0.9619</v>
@@ -1858,13 +1858,13 @@
         <v>0.5661</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3256</v>
+        <v>-0.2018</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0465</v>
+        <v>0.051</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2792</v>
+        <v>-0.2527</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MARISCAL GOMEZ</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.785</v>
+        <v>1.0353</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5045</v>
+        <v>1.468</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7196</v>
+        <v>-0.4327</v>
       </c>
       <c r="G19" t="n">
-        <v>3.0151</v>
+        <v>2.6539</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8491</v>
+        <v>1.091</v>
       </c>
       <c r="I19" t="n">
-        <v>3.8642</v>
+        <v>1.5629</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7514</v>
+        <v>2.1735</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5064</v>
+        <v>0.9141</v>
       </c>
       <c r="L19" t="n">
-        <v>3.2578</v>
+        <v>1.2595</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2637</v>
+        <v>0.4804</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3428</v>
+        <v>0.1769</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.3035</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.3774</v>
+        <v>-1.1322</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4379</v>
+        <v>-0.7508</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.8185</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5684</v>
+        <v>0.0677</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.547</v>
+        <v>-1.2452</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.547</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3533</v>
+        <v>0.2475</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3533</v>
+        <v>0.2475</v>
       </c>
       <c r="G20" t="n">
         <v>0.1299</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2234</v>
+        <v>0.1176</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2234</v>
+        <v>0.1176</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0382</v>
+        <v>-1.7202</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7128</v>
+        <v>-2.3948</v>
       </c>
       <c r="F21" t="n">
         <v>0.6746</v>
@@ -2092,10 +2092,10 @@
         <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0857</v>
+        <v>0.4037</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6647999999999999</v>
+        <v>-0.0172</v>
       </c>
       <c r="U21" t="n">
         <v>0.421</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
+          <t>A. GOMEZ-ARRONES MORGADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6895</v>
+        <v>-2.7916</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7741</v>
+        <v>-1.3147</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0846</v>
+        <v>-1.4769</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1804</v>
+        <v>0.1116</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0399</v>
+        <v>0.4993</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1404</v>
+        <v>-0.3877</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0618</v>
+        <v>1.2004</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.137</v>
+        <v>0.5494</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0752</v>
+        <v>0.651</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2421</v>
+        <v>-1.0888</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1769</v>
+        <v>-0.0501</v>
       </c>
       <c r="O22" t="n">
-        <v>0.06519999999999999</v>
+        <v>-1.0388</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.2644</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.0192</v>
+        <v>-1.887</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6054</v>
+        <v>-0.9032</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6931</v>
+        <v>-0.6282</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0877</v>
+        <v>-0.2751</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. GOMEZ-ARRONES MORGADO</t>
+          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0923</v>
+        <v>-2.9624</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5096</v>
+        <v>-3.6766</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5827</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1116</v>
+        <v>0.1804</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4993</v>
+        <v>0.0399</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3877</v>
+        <v>0.1404</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2004</v>
+        <v>-0.0618</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5494</v>
+        <v>-0.137</v>
       </c>
       <c r="L23" t="n">
-        <v>0.651</v>
+        <v>0.0752</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0888</v>
+        <v>0.2421</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0501</v>
+        <v>0.1769</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0388</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7548</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.887</v>
+        <v>-3.0192</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1322</v>
+        <v>0.7548</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2039</v>
+        <v>-0.8784</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.823</v>
+        <v>-0.5957</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3809</v>
+        <v>-0.2827</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>8.353399999999999</v>
+        <v>8.353599999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>5.504999999999999</v>
+        <v>5.505199999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8481</v>
+        <v>2.8483</v>
       </c>
       <c r="G24" t="n">
         <v>16.8397</v>
@@ -2296,7 +2296,7 @@
         <v>10.886</v>
       </c>
       <c r="I24" t="n">
-        <v>5.953799999999999</v>
+        <v>5.9538</v>
       </c>
       <c r="J24" t="n">
         <v>14.0901</v>
@@ -2311,7 +2311,7 @@
         <v>2.7498</v>
       </c>
       <c r="N24" t="n">
-        <v>0.7984</v>
+        <v>0.7984000000000002</v>
       </c>
       <c r="O24" t="n">
         <v>1.9511</v>
@@ -2326,10 +2326,10 @@
         <v>11.322</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.619</v>
+        <v>-6.6191</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.338100000000001</v>
+        <v>-5.337899999999999</v>
       </c>
       <c r="U24" t="n">
         <v>-1.2808</v>
